--- a/.cursor/02-系统级文档/单位系统/兵牌数值表.xlsx
+++ b/.cursor/02-系统级文档/单位系统/兵牌数值表.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -118,8 +118,26 @@
       <color rgb="00CC0000"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00375623"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -314,6 +332,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEF3EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
   </fills>
@@ -387,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -720,6 +743,97 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="39" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1168,512 +1282,512 @@
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="113" t="inlineStr">
         <is>
           <t>【国军 · 精锐中央军（德械师：88师/87师/36师）】</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="114" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="114" t="inlineStr">
         <is>
           <t>师部</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="80" t="inlineStr">
         <is>
           <t>国军·精锐</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="80" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="80" t="n">
         <v>20</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="80" t="n">
         <v>6</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="80" t="n">
         <v>80</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="80" t="n">
         <v>5</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="80" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="114" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="114" t="inlineStr">
         <is>
           <t>步兵团</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="80" t="inlineStr">
         <is>
           <t>国军·精锐</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="80" t="n">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="80" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="80" t="n">
         <v>25</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="80" t="n">
         <v>80</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="80" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="115" t="inlineStr">
         <is>
           <t>【国军 · 正规中央军】</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="116" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="116" t="inlineStr">
         <is>
           <t>师部</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="83" t="inlineStr">
         <is>
           <t>国军·正规</t>
         </is>
       </c>
-      <c r="D7" s="8" t="n">
+      <c r="D7" s="83" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="F7" s="83" t="n">
         <v>20</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="83" t="n">
         <v>65</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="83" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="8" t="n">
+      <c r="J7" s="83" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="116" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="116" t="inlineStr">
         <is>
           <t>步兵团</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="83" t="inlineStr">
         <is>
           <t>国军·正规</t>
         </is>
       </c>
-      <c r="D8" s="8" t="n">
+      <c r="D8" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="83" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="F8" s="83" t="n">
         <v>25</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="8" t="n">
+      <c r="H8" s="83" t="n">
         <v>65</v>
       </c>
-      <c r="I8" s="8" t="n">
+      <c r="I8" s="83" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="8" t="n">
+      <c r="J8" s="83" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="117" t="inlineStr">
         <is>
           <t>【国军 · 地方杂牌军】</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="118" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="118" t="inlineStr">
         <is>
           <t>师部</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="86" t="inlineStr">
         <is>
           <t>国军·杂牌</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="86" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="86" t="n">
         <v>18</v>
       </c>
-      <c r="G10" s="11" t="n">
+      <c r="G10" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="86" t="n">
         <v>50</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="86" t="n">
         <v>3</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="86" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="118" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="118" t="inlineStr">
         <is>
           <t>步兵团</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="86" t="inlineStr">
         <is>
           <t>国军·杂牌</t>
         </is>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="86" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="86" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="11" t="n">
+      <c r="F11" s="86" t="n">
         <v>22</v>
       </c>
-      <c r="G11" s="11" t="n">
+      <c r="G11" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="86" t="n">
         <v>50</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="86" t="n">
         <v>2</v>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="86" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="119" t="inlineStr">
         <is>
           <t>【日军 · 帝国陆军】</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="13" t="n">
+      <c r="A13" s="120" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="120" t="inlineStr">
         <is>
           <t>师团司令部</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="89" t="inlineStr">
         <is>
           <t>日军</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="89" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="14" t="n">
+      <c r="E13" s="89" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="89" t="n">
         <v>20</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="G13" s="89" t="n">
         <v>8</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="H13" s="89" t="n">
         <v>90</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="89" t="n">
         <v>5</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="J13" s="89" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="13" t="n">
+      <c r="A14" s="120" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>步兵联队（精锐）</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="B14" s="120" t="inlineStr">
+        <is>
+          <t>步兵联队（精锐，第3师团）</t>
+        </is>
+      </c>
+      <c r="C14" s="89" t="inlineStr">
         <is>
           <t>日军·精锐</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="89" t="n">
         <v>8</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="89" t="n">
         <v>7</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="89" t="n">
         <v>30</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="89" t="n">
         <v>5</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="89" t="n">
         <v>90</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="89" t="n">
         <v>5</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="89" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="13" t="n">
+      <c r="A15" s="120" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>步兵联队（普通）</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="B15" s="120" t="inlineStr">
+        <is>
+          <t>步兵联队（普通师团）</t>
+        </is>
+      </c>
+      <c r="C15" s="89" t="inlineStr">
         <is>
           <t>日军·普通</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="89" t="n">
         <v>7</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="89" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="89" t="n">
         <v>28</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="89" t="n">
         <v>4</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="89" t="n">
         <v>85</v>
       </c>
-      <c r="I15" s="14" t="n">
+      <c r="I15" s="89" t="n">
         <v>4</v>
       </c>
-      <c r="J15" s="14" t="n">
+      <c r="J15" s="89" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="13" t="n">
+      <c r="A16" s="120" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="120" t="inlineStr">
         <is>
           <t>海军陆战队</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="89" t="inlineStr">
         <is>
           <t>日军·特殊</t>
         </is>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="89" t="n">
         <v>9</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="89" t="n">
         <v>5</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="89" t="n">
         <v>25</v>
       </c>
-      <c r="G16" s="14" t="n">
+      <c r="G16" s="89" t="n">
         <v>6</v>
       </c>
-      <c r="H16" s="14" t="n">
+      <c r="H16" s="89" t="n">
         <v>92</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="89" t="n">
         <v>5</v>
       </c>
-      <c r="J16" s="14" t="n">
+      <c r="J16" s="89" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>【八路军 · 工农红军改编】</t>
+      <c r="A17" s="121" t="inlineStr">
+        <is>
+          <t>【八路军 · 工农红军改编（一师四团制）】</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="16" t="n">
+      <c r="A18" s="122" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="122" t="inlineStr">
         <is>
           <t>师部</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="92" t="inlineStr">
         <is>
           <t>八路军</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="17" t="n">
+      <c r="E18" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="F18" s="17" t="n">
+      <c r="F18" s="92" t="n">
         <v>35</v>
       </c>
-      <c r="G18" s="17" t="n">
+      <c r="G18" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="H18" s="17" t="n">
+      <c r="H18" s="92" t="n">
         <v>75</v>
       </c>
-      <c r="I18" s="17" t="n">
+      <c r="I18" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="17" t="n">
+      <c r="J18" s="92" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="16" t="n">
+      <c r="A19" s="122" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>步兵团（精锐）</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="inlineStr">
+      <c r="B19" s="122" t="inlineStr">
+        <is>
+          <t>步兵团（精锐，如685团）</t>
+        </is>
+      </c>
+      <c r="C19" s="92" t="inlineStr">
         <is>
           <t>八路军·精锐</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="92" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="17" t="n">
+      <c r="E19" s="92" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="17" t="n">
+      <c r="F19" s="92" t="n">
         <v>40</v>
       </c>
-      <c r="G19" s="17" t="n">
+      <c r="G19" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="H19" s="17" t="n">
+      <c r="H19" s="92" t="n">
         <v>75</v>
       </c>
-      <c r="I19" s="17" t="n">
+      <c r="I19" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="J19" s="17" t="n">
+      <c r="J19" s="92" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="16" t="n">
+      <c r="A20" s="122" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="122" t="inlineStr">
         <is>
           <t>步兵团（普通）</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
+      <c r="C20" s="92" t="inlineStr">
         <is>
           <t>八路军·普通</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="92" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="17" t="n">
+      <c r="E20" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="F20" s="17" t="n">
+      <c r="F20" s="92" t="n">
         <v>40</v>
       </c>
-      <c r="G20" s="17" t="n">
+      <c r="G20" s="92" t="n">
         <v>1</v>
       </c>
-      <c r="H20" s="17" t="n">
+      <c r="H20" s="92" t="n">
         <v>70</v>
       </c>
-      <c r="I20" s="17" t="n">
+      <c r="I20" s="92" t="n">
         <v>2</v>
       </c>
-      <c r="J20" s="17" t="n">
+      <c r="J20" s="92" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>注：工事防御加成另计（每级+1，最高4级，共需4天建满）；天气/夜间速度修正见天气系统速查表</t>
+      <c r="A21" s="123" t="inlineStr">
+        <is>
+          <t>注：工事防御加成另计（每级+1，满级4级共需4天）；天气/昼夜/整补速度修正见对应速查表</t>
         </is>
       </c>
     </row>
@@ -1697,27 +1811,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>兵牌状态系统速查表  （含作战意志体系）</t>
+          <t>兵牌状态系统速查表  （含作战意志 · 整补体系）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="67" t="inlineStr">
-        <is>
-          <t>▌ 一、状态效果汇总</t>
+      <c r="A2" s="124" t="inlineStr">
+        <is>
+          <t>▌ A  状态效果汇总</t>
         </is>
       </c>
     </row>
@@ -1739,22 +1854,27 @@
       </c>
       <c r="D3" s="68" t="inlineStr">
         <is>
-          <t>指令响应 / 移动</t>
+          <t>速度修正</t>
         </is>
       </c>
       <c r="E3" s="68" t="inlineStr">
         <is>
+          <t>指令响应 / 可补充</t>
+        </is>
+      </c>
+      <c r="F3" s="68" t="inlineStr">
+        <is>
           <t>备注</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
           <t>高昂 Inspired</t>
         </is>
       </c>
-      <c r="B4" s="69" t="inlineStr">
+      <c r="B4" s="125" t="inlineStr">
         <is>
           <t>士气≥80 且 兵力≥4</t>
         </is>
@@ -1764,24 +1884,29 @@
           <t>攻击+2</t>
         </is>
       </c>
-      <c r="D4" s="70" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="E4" s="70" t="inlineStr">
-        <is>
-          <t>金色标签；进攻冲击力倍增</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
+      <c r="D4" s="69" t="inlineStr">
+        <is>
+          <t>+20%</t>
+        </is>
+      </c>
+      <c r="E4" s="125" t="inlineStr">
+        <is>
+          <t>正常 / 否（前线）</t>
+        </is>
+      </c>
+      <c r="F4" s="125" t="inlineStr">
+        <is>
+          <t>进攻冲击力倍增</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="23" t="inlineStr">
         <is>
           <t>正常 Normal</t>
         </is>
       </c>
-      <c r="B5" s="52" t="inlineStr">
+      <c r="B5" s="126" t="inlineStr">
         <is>
           <t>士气在动摇线以上</t>
         </is>
@@ -1791,26 +1916,31 @@
           <t>无修正</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
-        <is>
-          <t>正常</t>
-        </is>
-      </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="D5" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="126" t="inlineStr">
+        <is>
+          <t>正常 / 否（前线）</t>
+        </is>
+      </c>
+      <c r="F5" s="126" t="inlineStr">
         <is>
           <t>默认状态</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
           <t>压制 Suppressed</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
-        <is>
-          <t>受炮击/密集射击事件</t>
+      <c r="B6" s="127" t="inlineStr">
+        <is>
+          <t>受炮击/密集射击事件触发</t>
         </is>
       </c>
       <c r="C6" s="71" t="inlineStr">
@@ -1818,410 +1948,601 @@
           <t>无法主动攻击</t>
         </is>
       </c>
-      <c r="D6" s="72" t="inlineStr">
-        <is>
-          <t>速度×0.5，受限</t>
-        </is>
-      </c>
-      <c r="E6" s="72" t="inlineStr">
-        <is>
-          <t>事件触发；约2-4小时自动消散</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
+      <c r="D6" s="71" t="inlineStr">
+        <is>
+          <t>×0.5</t>
+        </is>
+      </c>
+      <c r="E6" s="127" t="inlineStr">
+        <is>
+          <t>受限 / 否</t>
+        </is>
+      </c>
+      <c r="F6" s="127" t="inlineStr">
+        <is>
+          <t>2-4小时后自动消散</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" s="27" t="inlineStr">
         <is>
           <t>动摇 Shaken</t>
         </is>
       </c>
-      <c r="B7" s="73" t="inlineStr">
-        <is>
-          <t>达到该等级动摇临界（见下表）</t>
+      <c r="B7" s="128" t="inlineStr">
+        <is>
+          <t>达到该等级动摇临界</t>
         </is>
       </c>
       <c r="C7" s="73" t="inlineStr">
         <is>
-          <t>攻击-1，防御-1</t>
-        </is>
-      </c>
-      <c r="D7" s="74" t="inlineStr">
-        <is>
-          <t>速度-20%，受限；每小时有概率自动后退1格</t>
-        </is>
-      </c>
-      <c r="E7" s="74" t="inlineStr">
-        <is>
-          <t>橙色闪烁</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
+          <t>攻-1 防-1</t>
+        </is>
+      </c>
+      <c r="D7" s="73" t="inlineStr">
+        <is>
+          <t>-20%</t>
+        </is>
+      </c>
+      <c r="E7" s="128" t="inlineStr">
+        <is>
+          <t>受限 / 否</t>
+        </is>
+      </c>
+      <c r="F7" s="128" t="inlineStr">
+        <is>
+          <t>每小时有概率自动后退1格</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" s="29" t="inlineStr">
         <is>
           <t>溃散 Routed</t>
         </is>
       </c>
-      <c r="B8" s="75" t="inlineStr">
-        <is>
-          <t>达到该等级崩溃条件（见下表）</t>
+      <c r="B8" s="129" t="inlineStr">
+        <is>
+          <t>达到该等级崩溃条件</t>
         </is>
       </c>
       <c r="C8" s="75" t="inlineStr">
         <is>
-          <t>无法攻击，防御-2</t>
-        </is>
-      </c>
-      <c r="D8" s="76" t="inlineStr">
-        <is>
-          <t>强制向后撤退×0.7</t>
-        </is>
-      </c>
-      <c r="E8" s="76" t="inlineStr">
-        <is>
-          <t>红色闪烁；撤离后缓慢恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="77" t="inlineStr">
-        <is>
-          <t>★ 歼灭：兵力值降至 0 → 兵牌直接从棋盘移除（成建制消灭），无过渡状态。</t>
-        </is>
-      </c>
-      <c r="B9" s="102" t="n"/>
-      <c r="C9" s="102" t="n"/>
-      <c r="D9" s="102" t="n"/>
-      <c r="E9" s="103" t="n"/>
-    </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="67" t="inlineStr">
-        <is>
-          <t>▌ 二、作战意志（Combat Will）— 各等级崩溃临界值与士气恢复速度</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+          <t>无法攻击 防-2</t>
+        </is>
+      </c>
+      <c r="D8" s="75" t="inlineStr">
+        <is>
+          <t>×0.7(强制后退)</t>
+        </is>
+      </c>
+      <c r="E8" s="129" t="inlineStr">
+        <is>
+          <t>丧失 / 否（撤退中）</t>
+        </is>
+      </c>
+      <c r="F8" s="129" t="inlineStr">
+        <is>
+          <t>须先撤离才可整补</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="130" t="inlineStr">
+        <is>
+          <t>后撤整补 Recup.</t>
+        </is>
+      </c>
+      <c r="B9" s="131" t="inlineStr">
+        <is>
+          <t>脱离前线≥4格+非战斗+补给≥1</t>
+        </is>
+      </c>
+      <c r="C9" s="55" t="inlineStr">
+        <is>
+          <t>无修正</t>
+        </is>
+      </c>
+      <c r="D9" s="55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="131" t="inlineStr">
+        <is>
+          <t>正常 / 是</t>
+        </is>
+      </c>
+      <c r="F9" s="131" t="inlineStr">
+        <is>
+          <t>自动恢复兵力与士气</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="77" t="inlineStr">
+        <is>
+          <t>★ 歼灭：兵力值降至 0 → 兵牌直接移除（成建制消灭），无过渡状态。</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="124" t="inlineStr">
+        <is>
+          <t>▌ B  作战意志（Combat Will）— 各等级崩溃临界值与士气恢复速度</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>部队等级</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>动摇条件（→Shaken）</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>崩溃条件（→Routed）</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>士气恢复速度
-（/小时，非战斗休整）</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>士气恢复
+(/小时，非战斗)</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>整补速度修正
+(Strength/天)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>设计意图</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="78" t="inlineStr">
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="78" t="inlineStr">
         <is>
           <t>国军·精锐</t>
         </is>
       </c>
-      <c r="B13" s="79" t="inlineStr">
+      <c r="B14" s="132" t="inlineStr">
         <is>
           <t>士气 &lt; 40</t>
         </is>
       </c>
-      <c r="C13" s="79" t="inlineStr">
+      <c r="C14" s="132" t="inlineStr">
         <is>
           <t>（兵力≤1 且 士气≤30）
 或 士气=0</t>
         </is>
       </c>
-      <c r="D13" s="80" t="inlineStr">
-        <is>
-          <t>+2.5 / 小时</t>
-        </is>
-      </c>
-      <c r="E13" s="79" t="inlineStr">
+      <c r="D14" s="80" t="inlineStr">
+        <is>
+          <t>+2.5</t>
+        </is>
+      </c>
+      <c r="E14" s="80" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="F14" s="132" t="inlineStr">
         <is>
           <t>德械精兵，死战到底</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="81" t="inlineStr">
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="81" t="inlineStr">
         <is>
           <t>国军·正规</t>
         </is>
       </c>
-      <c r="B14" s="82" t="inlineStr">
+      <c r="B15" s="133" t="inlineStr">
         <is>
           <t>士气 &lt; 45</t>
         </is>
       </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="C15" s="133" t="inlineStr">
         <is>
           <t>兵力≤1  或  士气≤15</t>
         </is>
       </c>
-      <c r="D14" s="83" t="inlineStr">
-        <is>
-          <t>+1.5 / 小时</t>
-        </is>
-      </c>
-      <c r="E14" s="82" t="inlineStr">
-        <is>
-          <t>有训练基础，但难承重大伤亡</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="84" t="inlineStr">
+      <c r="D15" s="83" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="E15" s="83" t="inlineStr">
+        <is>
+          <t>×0.8</t>
+        </is>
+      </c>
+      <c r="F15" s="133" t="inlineStr">
+        <is>
+          <t>有训练基础，难承重大伤亡</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="84" t="inlineStr">
         <is>
           <t>国军·杂牌</t>
         </is>
       </c>
-      <c r="B15" s="85" t="inlineStr">
+      <c r="B16" s="134" t="inlineStr">
         <is>
           <t>士气 &lt; 50</t>
         </is>
       </c>
-      <c r="C15" s="85" t="inlineStr">
+      <c r="C16" s="134" t="inlineStr">
         <is>
           <t>兵力≤2（约50%）
-或  士气≤25</t>
-        </is>
-      </c>
-      <c r="D15" s="86" t="inlineStr">
-        <is>
-          <t>+0.5 / 小时</t>
-        </is>
-      </c>
-      <c r="E15" s="85" t="inlineStr">
-        <is>
-          <t>伤亡过半即崩溃，恢复极慢</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="87" t="inlineStr">
+或 士气≤25</t>
+        </is>
+      </c>
+      <c r="D16" s="86" t="inlineStr">
+        <is>
+          <t>+0.5</t>
+        </is>
+      </c>
+      <c r="E16" s="86" t="inlineStr">
+        <is>
+          <t>×0.5</t>
+        </is>
+      </c>
+      <c r="F16" s="134" t="inlineStr">
+        <is>
+          <t>伤亡过半即崩，恢复极慢</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="87" t="inlineStr">
         <is>
           <t>日军</t>
         </is>
       </c>
-      <c r="B16" s="88" t="inlineStr">
+      <c r="B17" s="135" t="inlineStr">
         <is>
           <t>士气 &lt; 35</t>
         </is>
       </c>
-      <c r="C16" s="88" t="inlineStr">
+      <c r="C17" s="135" t="inlineStr">
         <is>
           <t>（兵力≤1 且 士气≤20）
 或 士气=0</t>
         </is>
       </c>
-      <c r="D16" s="89" t="inlineStr">
-        <is>
-          <t>+3.0 / 小时</t>
-        </is>
-      </c>
-      <c r="E16" s="88" t="inlineStr">
-        <is>
-          <t>武士道精神，极难被单纯伤亡击溃</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="90" t="inlineStr">
+      <c r="D17" s="89" t="inlineStr">
+        <is>
+          <t>+3.0</t>
+        </is>
+      </c>
+      <c r="E17" s="89" t="inlineStr">
+        <is>
+          <t>×1.2</t>
+        </is>
+      </c>
+      <c r="F17" s="135" t="inlineStr">
+        <is>
+          <t>武士道精神，极难被伤亡击溃</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="90" t="inlineStr">
         <is>
           <t>八路军·精锐</t>
         </is>
       </c>
-      <c r="B17" s="91" t="inlineStr">
+      <c r="B18" s="136" t="inlineStr">
         <is>
           <t>士气 &lt; 40</t>
         </is>
       </c>
-      <c r="C17" s="91" t="inlineStr">
+      <c r="C18" s="136" t="inlineStr">
         <is>
           <t>兵力≤1  或  士气≤10</t>
         </is>
       </c>
-      <c r="D17" s="92" t="inlineStr">
-        <is>
-          <t>+2.0 / 小时</t>
-        </is>
-      </c>
-      <c r="E17" s="91" t="inlineStr">
+      <c r="D18" s="92" t="inlineStr">
+        <is>
+          <t>+2.0</t>
+        </is>
+      </c>
+      <c r="E18" s="92" t="inlineStr">
+        <is>
+          <t>×1.0</t>
+        </is>
+      </c>
+      <c r="F18" s="136" t="inlineStr">
         <is>
           <t>政委制度维系意志</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="93" t="inlineStr">
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="93" t="inlineStr">
         <is>
           <t>八路军·普通</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
+      <c r="B19" s="137" t="inlineStr">
         <is>
           <t>士气 &lt; 45</t>
         </is>
       </c>
-      <c r="C18" s="94" t="inlineStr">
+      <c r="C19" s="137" t="inlineStr">
         <is>
           <t>兵力≤1  或  士气≤20</t>
         </is>
       </c>
-      <c r="D18" s="95" t="inlineStr">
-        <is>
-          <t>+1.5 / 小时</t>
-        </is>
-      </c>
-      <c r="E18" s="94" t="inlineStr">
+      <c r="D19" s="95" t="inlineStr">
+        <is>
+          <t>+1.5</t>
+        </is>
+      </c>
+      <c r="E19" s="95" t="inlineStr">
+        <is>
+          <t>×0.8</t>
+        </is>
+      </c>
+      <c r="F19" s="137" t="inlineStr">
         <is>
           <t>游击队，兵力告急时主动撤退</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="67" t="inlineStr">
-        <is>
-          <t>▌ 三、士气恢复环境修正（非战斗状态下持续超过1小时生效）</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="50" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="124" t="inlineStr">
+        <is>
+          <t>▌ C  后撤整补（Recuperating）— 触发条件与补充规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="50" t="inlineStr">
+        <is>
+          <t>触发条件（三项同时满足）</t>
+        </is>
+      </c>
+      <c r="B22" s="50" t="inlineStr"/>
+      <c r="C22" s="50" t="inlineStr"/>
+      <c r="D22" s="50" t="inlineStr">
+        <is>
+          <t>补充规则项</t>
+        </is>
+      </c>
+      <c r="E22" s="50" t="inlineStr"/>
+      <c r="F22" s="50" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="138" t="inlineStr">
+        <is>
+          <t>① 非战斗状态</t>
+        </is>
+      </c>
+      <c r="B23" s="139" t="inlineStr">
+        <is>
+          <t>未受攻击 且 未主动攻击</t>
+        </is>
+      </c>
+      <c r="D23" s="140" t="inlineStr">
+        <is>
+          <t>兵力恢复速度</t>
+        </is>
+      </c>
+      <c r="E23" s="134" t="inlineStr">
+        <is>
+          <t>+1 点 Strength / 天（代表约20%满编兵力）</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="138" t="inlineStr">
+        <is>
+          <t>② 脱离前线</t>
+        </is>
+      </c>
+      <c r="B24" s="139" t="inlineStr">
+        <is>
+          <t>距最近敌军兵牌 ≥ 4 格</t>
+        </is>
+      </c>
+      <c r="D24" s="140" t="inlineStr">
+        <is>
+          <t>补给消耗</t>
+        </is>
+      </c>
+      <c r="E24" s="134" t="inlineStr">
+        <is>
+          <t>每恢复 1点 Strength 消耗 Supply 1点</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="138" t="inlineStr">
+        <is>
+          <t>③ 有补给来源</t>
+        </is>
+      </c>
+      <c r="B25" s="139" t="inlineStr">
+        <is>
+          <t>Supply ≥ 1 且 与后方补给基地路径连通</t>
+        </is>
+      </c>
+      <c r="D25" s="140" t="inlineStr">
+        <is>
+          <t>士气联动</t>
+        </is>
+      </c>
+      <c r="E25" s="134" t="inlineStr">
+        <is>
+          <t>整补期间士气恢复速度 ×2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="141" t="inlineStr"/>
+      <c r="B26" s="141" t="inlineStr"/>
+      <c r="C26" s="103" t="n"/>
+      <c r="D26" s="140" t="inlineStr">
+        <is>
+          <t>中断条件</t>
+        </is>
+      </c>
+      <c r="E26" s="134" t="inlineStr">
+        <is>
+          <t>进入敌军4格范围内 或 受到攻击 → 立即中断</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="141" t="inlineStr"/>
+      <c r="B27" s="141" t="inlineStr"/>
+      <c r="C27" s="103" t="n"/>
+      <c r="D27" s="140" t="inlineStr">
+        <is>
+          <t>溃散限制</t>
+        </is>
+      </c>
+      <c r="E27" s="134" t="inlineStr">
+        <is>
+          <t>溃散状态不可整补，须先解除溃散</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="124" t="inlineStr">
+        <is>
+          <t>▌ D  士气恢复环境修正（非战斗状态下超过1小时生效）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>环境条件</t>
         </is>
       </c>
-      <c r="B21" s="102" t="n"/>
-      <c r="C21" s="103" t="n"/>
-      <c r="D21" s="50" t="inlineStr">
-        <is>
-          <t>士气恢复速度修正</t>
-        </is>
-      </c>
-      <c r="E21" s="103" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="96" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr"/>
+      <c r="C30" s="20" t="inlineStr"/>
+      <c r="D30" s="20" t="inlineStr"/>
+      <c r="E30" s="20" t="inlineStr"/>
+      <c r="F30" s="20" t="inlineStr">
+        <is>
+          <t>修正系数</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="131" t="inlineStr">
         <is>
           <t>在师部/旅部指挥范围内</t>
         </is>
       </c>
-      <c r="B22" s="102" t="n"/>
-      <c r="C22" s="103" t="n"/>
-      <c r="D22" s="96" t="inlineStr">
-        <is>
-          <t>基础速度 × 2.0</t>
-        </is>
-      </c>
-      <c r="E22" s="103" t="n"/>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="97" t="inlineStr">
+      <c r="F31" s="54" t="inlineStr">
+        <is>
+          <t>×2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="131" t="inlineStr">
         <is>
           <t>补给充足（Supply ≥ 3）</t>
         </is>
       </c>
-      <c r="B23" s="102" t="n"/>
-      <c r="C23" s="103" t="n"/>
-      <c r="D23" s="97" t="inlineStr">
-        <is>
-          <t>基础速度 × 1.5</t>
-        </is>
-      </c>
-      <c r="E23" s="103" t="n"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="98" t="inlineStr">
+      <c r="F32" s="55" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="131" t="inlineStr">
+        <is>
+          <t>夜间休整（停止行军 ≥ 8小时）</t>
+        </is>
+      </c>
+      <c r="F33" s="55" t="inlineStr">
+        <is>
+          <t>×1.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="127" t="inlineStr">
+        <is>
+          <t>溃散状态中</t>
+        </is>
+      </c>
+      <c r="F34" s="142" t="inlineStr">
+        <is>
+          <t>×0.3（极慢，须先撤离战场）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="129" t="inlineStr">
         <is>
           <t>补给断绝（Supply = 0）</t>
         </is>
       </c>
-      <c r="B24" s="102" t="n"/>
-      <c r="C24" s="103" t="n"/>
-      <c r="D24" s="99" t="inlineStr">
-        <is>
-          <t>× 0（无法自然恢复），且每天额外 -8</t>
-        </is>
-      </c>
-      <c r="E24" s="103" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="97" t="inlineStr">
-        <is>
-          <t>夜间休整停止行军超过8小时</t>
-        </is>
-      </c>
-      <c r="B25" s="102" t="n"/>
-      <c r="C25" s="103" t="n"/>
-      <c r="D25" s="97" t="inlineStr">
-        <is>
-          <t>基础速度 × 1.5</t>
-        </is>
-      </c>
-      <c r="E25" s="103" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="100" t="inlineStr">
-        <is>
-          <t>溃散状态中</t>
-        </is>
-      </c>
-      <c r="B26" s="102" t="n"/>
-      <c r="C26" s="103" t="n"/>
-      <c r="D26" s="100" t="inlineStr">
-        <is>
-          <t>× 0.3（极慢，需先撤离战场）</t>
-        </is>
-      </c>
-      <c r="E26" s="103" t="n"/>
-    </row>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="101" t="inlineStr">
-        <is>
-          <t>溃散解除条件：距离最近敌军 ≥ 4格（安全后方）且士气自然回升到该等级动摇临界值以上</t>
-        </is>
-      </c>
-      <c r="B27" s="102" t="n"/>
-      <c r="C27" s="102" t="n"/>
-      <c r="D27" s="102" t="n"/>
-      <c r="E27" s="103" t="n"/>
+      <c r="F35" s="143" t="inlineStr">
+        <is>
+          <t>×0（不可自然恢复）且每天额外 -8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="16" customHeight="1">
+      <c r="A36" s="123" t="inlineStr">
+        <is>
+          <t>溃散解除条件：距最近敌军 ≥ 4格（安全后方）且士气自然回升至该等级动摇临界值以上</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="D21:E21"/>
+  <mergeCells count="25">
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A24"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A25"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A33:E33"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2241,7 +2562,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2348,7 +2669,7 @@
       </c>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="112" t="inlineStr">
+      <c r="A5" s="123" t="inlineStr">
         <is>
           <t>昼夜说明：白天约14小时（正常行军）；夜间约10小时（行军×0.5，八路军除外）；夜间侦察范围缩小</t>
         </is>
